--- a/week02/data_compareSort.xlsx
+++ b/week02/data_compareSort.xlsx
@@ -5,16 +5,24 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WD\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WD\Desktop\algorithm\week02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E14EFD-378C-425F-9D8E-8DE4300C654E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B9D4FC-1EE9-4134-842A-32225280B1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18300" yWindow="2985" windowWidth="17670" windowHeight="14250" xr2:uid="{214B3055-B83F-4E0B-AC70-A79C0459B4B7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{214B3055-B83F-4E0B-AC70-A79C0459B4B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$45:$A$46</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$A$47:$A$57</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$B$45:$B$46</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$47:$B$57</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$C$45:$C$46</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$C$47:$C$57</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="111">
   <si>
     <t>A 실험 결과</t>
   </si>
@@ -310,14 +318,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>4000~8000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>8000~16000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>16000~32000</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -343,6 +343,138 @@
   </si>
   <si>
     <t>실험 B</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>256000번 실행</t>
+  </si>
+  <si>
+    <t>5000번 실행</t>
+  </si>
+  <si>
+    <t>10000번 실행</t>
+  </si>
+  <si>
+    <t>15000번 실행</t>
+  </si>
+  <si>
+    <t>선택정렬: 42.646100000000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:    28.490200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 77.169800000000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:     0.015300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 57.152900000000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:    51.850000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 10.992900000000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:     8.881400</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 20.089900000000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:     0.007200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 13.751000000000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:    12.742100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 87.357500000000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 164.500800000000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:    60.469500</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:     0.021100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 135.302700000000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:   111.664400</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 26101.401699999999</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬: 16761.015300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 62985.170700000002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬:     0.455300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택정렬: 55569.639999999999</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입정렬: 41101.481800</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000~5000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000~8000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8000~10000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000~15000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15000~16000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>128000~256000</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -444,7 +576,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -452,9 +584,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2">
@@ -520,6 +649,7 @@
               <a:rPr lang="en-US"/>
               <a:t>A</a:t>
             </a:r>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -555,12 +685,13 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$45:$B$46</c:f>
@@ -576,36 +707,78 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="6"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:round/>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$47:$A$54</c:f>
+              <c:f>Sheet1!$A$47:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -616,29 +789,41 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>16000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>32000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>64000</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$47:$B$54</c:f>
+              <c:f>Sheet1!$B$47:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.86260000000000003</c:v>
                 </c:pt>
@@ -649,33 +834,44 @@
                   <c:v>7.2435</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>10.992900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>25.505199999999999</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>42.646099999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>87.357500000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>102.5004</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>395.53519999999997</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>1647.6356000000001</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>6449.5387000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>26101.4016999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-22BA-4684-B91A-40F71937F4A3}"/>
+              <c16:uniqueId val="{00000001-4FEC-42B3-AC87-8C00BD78E47B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="2"/>
+          <c:order val="2"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$C$45:$C$46</c:f>
@@ -691,36 +887,78 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="6"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:round/>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$47:$A$54</c:f>
+              <c:f>Sheet1!$A$47:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -731,29 +969,41 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>16000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>32000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>64000</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$47:$C$54</c:f>
+              <c:f>Sheet1!$C$47:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.70030000000000003</c:v>
                 </c:pt>
@@ -764,43 +1014,261 @@
                   <c:v>5.2759</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>8.8813999999999993</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>19.936499999999999</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>28.490200000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60.469499999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>69.941699999999997</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>271.66899999999998</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>1038.0461</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>4179.1432000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16761.015299999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-22BA-4684-B91A-40F71937F4A3}"/>
+              <c16:uniqueId val="{00000002-4FEC-42B3-AC87-8C00BD78E47B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="170892560"/>
-        <c:axId val="81870768"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="170892560"/>
+        <c:gapWidth val="444"/>
+        <c:overlap val="-90"/>
+        <c:axId val="258745919"/>
+        <c:axId val="2054714543"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$45:$A$46</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>실험A</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>n</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="50000"/>
+                              <a:lumOff val="50000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="ko-KR"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$47:$A$58</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>32000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>64000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>128000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>256000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$47:$A$58</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>32000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>64000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>128000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>256000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-4FEC-42B3-AC87-8C00BD78E47B}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="258745919"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -842,7 +1310,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -857,71 +1325,27 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81870768"/>
+        <c:crossAx val="2054714543"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="81870768"/>
+        <c:axId val="2054714543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ko-KR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="170892560"/>
+        <c:crossAx val="258745919"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1047,7 +1471,6 @@
               <a:rPr lang="en-US" altLang="ko-KR"/>
               <a:t>B</a:t>
             </a:r>
-            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1083,172 +1506,97 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$F$45:$F$46</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>실험B</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>선택정렬(ms)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="22225" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$47:$E$54</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>32000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>64000</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>128000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$F$47:$F$54</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1.0325</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.9948999999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14.5204</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>53.217199999999998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>183.66059999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>761.73990000000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3083.2289000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>13345.0816</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D2A1-4836-9708-D0F63C7A1466}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$45:$G$46</c:f>
+              <c:f>Sheet1!$F$46</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>실험B</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>삽입정렬(ms)</c:v>
+                  <c:v>선택정렬(ms)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="6"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:round/>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$E$47:$E$54</c:f>
+              <c:f>Sheet1!$E$47:$E$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -1259,29 +1607,218 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>16000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>32000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>64000</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$47:$G$54</c:f>
+              <c:f>Sheet1!$F$47:$F$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1.0325</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.9948999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.5204</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.0899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.217199999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>77.169799999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>164.5008</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>183.66059999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>761.73990000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3083.2289000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13345.0816</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>62985.170700000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D6C5-4D02-8D3F-B1D2E1E7A8C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>삽입정렬(ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$E$47:$E$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$47:$G$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2E-3</c:v>
                 </c:pt>
@@ -1292,43 +1829,258 @@
                   <c:v>6.1000000000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>7.1999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>1.1900000000000001E-2</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>1.5299999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.1100000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>2.3699999999999999E-2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>8.1299999999999997E-2</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>9.3200000000000005E-2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>0.27579999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.45529999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D2A1-4836-9708-D0F63C7A1466}"/>
+              <c16:uniqueId val="{00000002-D6C5-4D02-8D3F-B1D2E1E7A8C9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="171306432"/>
-        <c:axId val="81918288"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="171306432"/>
+        <c:gapWidth val="444"/>
+        <c:overlap val="-90"/>
+        <c:axId val="258682815"/>
+        <c:axId val="2054664623"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$E$46</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>n</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="50000"/>
+                              <a:lumOff val="50000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="ko-KR"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$E$47:$E$58</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>32000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>64000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>128000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>256000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$E$47:$E$58</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>32000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>64000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>128000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>256000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-D6C5-4D02-8D3F-B1D2E1E7A8C9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="258682815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1370,7 +2122,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1385,71 +2137,27 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81918288"/>
+        <c:crossAx val="2054664623"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="81918288"/>
+        <c:axId val="2054664623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ko-KR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="171306432"/>
+        <c:crossAx val="258682815"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1575,6 +2283,7 @@
               <a:rPr lang="en-US" altLang="ko-KR"/>
               <a:t>C</a:t>
             </a:r>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1610,166 +2319,100 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$J$46</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>선택정렬(ms)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="22225" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$47:$I$54</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>32000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>64000</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>128000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$J$47:$J$54</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0.6361</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.2241</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.4702000000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>36.610199999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>145.6395</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>582.25909999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2307.3020999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9953.6134000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9920-4D3D-B3E2-7169F35A6650}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$K$46</c:f>
+              <c:f>Sheet1!$J$45:$J$46</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>삽입정렬(ms)</c:v>
+                  <c:v>실험C</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>선택정렬(ms)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="6"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:round/>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$I$47:$I$54</c:f>
+              <c:f>Sheet1!$I$47:$I$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -1780,29 +2423,221 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>16000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>32000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>64000</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$47:$K$54</c:f>
+              <c:f>Sheet1!$J$47:$J$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.6361</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2241</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.4702000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.750999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.610199999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>57.152900000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>135.30269999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>145.6395</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>582.25909999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2307.3020999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9953.6134000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>55569.639999999898</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C03E-44CF-87FA-B47B59D2DC16}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$45:$K$46</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>실험C</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>삽입정렬(ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$I$47:$I$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$47:$K$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.0998000000000001</c:v>
                 </c:pt>
@@ -1813,43 +2648,261 @@
                   <c:v>8.6060999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>12.742100000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>32.941600000000001</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>51.85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>111.6644</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>132.96340000000001</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>514.17470000000003</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>2096.8153000000002</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>8372.7314999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>41101.481800000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9920-4D3D-B3E2-7169F35A6650}"/>
+              <c16:uniqueId val="{00000002-C03E-44CF-87FA-B47B59D2DC16}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="178283424"/>
-        <c:axId val="81888528"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="178283424"/>
+        <c:gapWidth val="444"/>
+        <c:overlap val="-90"/>
+        <c:axId val="703491839"/>
+        <c:axId val="2054762063"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$I$45:$I$46</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>실험C</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>n</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="50000"/>
+                              <a:lumOff val="50000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="ko-KR"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$I$47:$I$58</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>32000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>64000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>128000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>256000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$I$47:$I$58</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>32000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>64000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>128000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>256000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-C03E-44CF-87FA-B47B59D2DC16}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="703491839"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1891,7 +2944,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1906,71 +2959,27 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81888528"/>
+        <c:crossAx val="2054762063"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="81888528"/>
+        <c:axId val="2054762063"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ko-KR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="178283424"/>
+        <c:crossAx val="703491839"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2025,6 +3034,1728 @@
   <c:spPr>
     <a:solidFill>
       <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>실험 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>A</a:t>
+            </a:r>
+            <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$45:$B$46</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>실험A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>선택정렬(ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$47:$A$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$47:$B$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.86260000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0278999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.2435</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.992900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.505199999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>42.646099999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>87.357500000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>102.5004</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>395.53519999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1647.6356000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6449.5387000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>26101.4016999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8E9F-441F-AB35-7C53344C5480}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$45:$C$46</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>실험A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>삽입정렬(ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$47:$A$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$47:$C$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.70030000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.4186000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.2759</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.8813999999999993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.936499999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28.490200000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60.469499999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>69.941699999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>271.66899999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1038.0461</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4179.1432000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16761.015299999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8E9F-441F-AB35-7C53344C5480}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="103765615"/>
+        <c:axId val="2054781743"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="103765615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054781743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2054781743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="103765615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>실험 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>B</a:t>
+            </a:r>
+            <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$45:$F$46</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>실험B</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>선택정렬(ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$47:$E$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$47:$F$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1.0325</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.9948999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.5204</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.0899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.217199999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>77.169799999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>164.5008</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>183.66059999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>761.73990000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3083.2289000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13345.0816</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>62985.170700000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FABB-4653-AB28-A54E6F67F5CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$45:$G$46</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>실험B</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>삽입정렬(ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$47:$E$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$47:$G$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.1000000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.1999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1900000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5299999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.1100000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.3699999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.1299999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.3200000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.27579999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.45529999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FABB-4653-AB28-A54E6F67F5CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="252564143"/>
+        <c:axId val="2054763503"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="252564143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054763503"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2054763503"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="252564143"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>실험 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>C</a:t>
+            </a:r>
+            <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$J$45:$J$46</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>실험C</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>선택정렬(ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$47:$I$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$47:$J$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.6361</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2241</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.4702000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.750999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.610199999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>57.152900000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>135.30269999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>145.6395</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>582.25909999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2307.3020999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9953.6134000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>55569.639999999898</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3C64-4D8E-8DB8-514C28F71C87}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$45:$K$46</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>실험C</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>삽입정렬(ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$47:$I$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>256000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$47:$K$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1.0998000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1716000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.6060999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.742100000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32.941600000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>51.85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>111.6644</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>132.96340000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>514.17470000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2096.8153000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8372.7314999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>41101.481800000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3C64-4D8E-8DB8-514C28F71C87}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="114072287"/>
+        <c:axId val="2054715983"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="114072287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054715983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2054715983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="114072287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -2175,8 +4906,128 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="241">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2210,7 +5061,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -2246,6 +5097,9 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -2504,8 +5358,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2621,10 +5475,11 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2696,7 +5551,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="241">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2730,7 +5585,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -2766,6 +5621,9 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -3024,8 +5882,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -3141,10 +5999,11 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3216,7 +6075,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="241">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3250,7 +6109,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -3286,6 +6145,9 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -3544,8 +6406,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -3661,10 +6523,11 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3731,6 +6594,1554 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -3741,21 +8152,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>186018</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>582706</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>161365</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="차트 3">
+        <xdr:cNvPr id="13" name="차트 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{812BCDEF-6C78-0999-2602-A36DE0DC718C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DA55048-A1A0-B996-0656-0C2C3C105C2E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3775,23 +8186,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1131794</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>186018</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>313764</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>161365</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="차트 4">
+        <xdr:cNvPr id="14" name="차트 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDEF9E00-AC3E-C4BC-813B-FDE3541FD006}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1399E08F-132F-C22A-6871-34FD94A65B3A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3811,23 +8222,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>496661</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>172810</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>924484</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>197223</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>306161</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>58510</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>16808</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>172570</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="차트 5">
+        <xdr:cNvPr id="15" name="차트 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB3984D2-204F-DF56-6E7D-8D81CB45EC94}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{379655A7-DDA4-5233-4254-9B32EDBE2164}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3840,6 +8251,114 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>62753</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>582706</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="16" name="차트 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF23CAC8-294C-23B5-907B-56331610AED1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1182220</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>73958</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>364190</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>49305</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="17" name="차트 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D05A8C5-B3B5-6DC3-46EF-E544D648826C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>958102</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>208429</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>50426</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>183776</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="18" name="차트 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7819918-DC4C-EF6B-4E1A-88DD14DDB64C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4165,7 +8684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549FA785-882B-477F-9666-0E15ECF9EBBD}">
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:U104"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" style="1" customWidth="1"/>
@@ -4183,476 +8702,476 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4">
+      <c r="A1" s="3">
         <v>1000</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3">
         <v>2000</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3">
         <v>4000</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3">
         <v>8000</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4">
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3">
         <v>16000</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4" t="s">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4" t="s">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4" t="s">
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4" t="s">
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4" t="s">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4" t="s">
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4" t="s">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4" t="s">
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4" t="s">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4" t="s">
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4" t="s">
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4" t="s">
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
     </row>
-    <row r="17" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4" t="s">
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4" t="s">
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4" t="s">
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4" t="s">
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4" t="s">
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4" t="s">
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
     </row>
-    <row r="19" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4" t="s">
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4" t="s">
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4" t="s">
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
     </row>
-    <row r="20" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4" t="s">
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4" t="s">
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4" t="s">
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
     </row>
-    <row r="21" spans="1:15" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
@@ -4669,7 +9188,7 @@
       <c r="N21"/>
       <c r="O21"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -4686,428 +9205,556 @@
       <c r="N22"/>
       <c r="O22"/>
     </row>
-    <row r="23" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
+    <row r="23" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
         <v>32000</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3">
         <v>64000</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4">
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3">
         <v>128000</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3">
+        <v>256000</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="Q23" s="1">
+        <v>10000</v>
+      </c>
+      <c r="U23" s="1">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="24" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
+    <row r="24" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
     </row>
-    <row r="25" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="Q25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4" t="s">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4" t="s">
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="Q26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="27" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4" t="s">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4" t="s">
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="Q27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>93</v>
+      </c>
     </row>
-    <row r="28" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4" t="s">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4" t="s">
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="Q28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
-    <row r="29" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
+    <row r="29" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
     </row>
-    <row r="30" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
+    <row r="30" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
     </row>
-    <row r="31" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
+    <row r="31" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
     </row>
-    <row r="32" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4" t="s">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4" t="s">
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="Q32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4" t="s">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4" t="s">
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="Q33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="34" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4" t="s">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4" t="s">
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="Q34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
-    <row r="35" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4" t="s">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4" t="s">
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="Q35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="36" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
+    <row r="36" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
     </row>
-    <row r="37" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
+    <row r="37" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
     </row>
-    <row r="38" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
+    <row r="38" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
     </row>
-    <row r="39" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4" t="s">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4" t="s">
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="Q39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="40" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4" t="s">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4" t="s">
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="Q40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="41" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4" t="s">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4" t="s">
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="Q41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>97</v>
+      </c>
     </row>
-    <row r="42" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:21" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4" t="s">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4" t="s">
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="Q42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="43" spans="1:15" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="G43" s="3"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>18</v>
       </c>
@@ -5124,7 +9771,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>13</v>
       </c>
@@ -5153,7 +9800,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>1000</v>
       </c>
@@ -5182,7 +9829,7 @@
         <v>1.0998000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>2000</v>
       </c>
@@ -5242,438 +9889,694 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="B50" s="2">
-        <v>25.505199999999999</v>
+        <v>10.992900000000001</v>
       </c>
       <c r="C50" s="2">
-        <v>19.936499999999999</v>
+        <v>8.8813999999999993</v>
       </c>
       <c r="E50" s="2">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="F50" s="2">
-        <v>53.217199999999998</v>
+        <v>20.0899</v>
       </c>
       <c r="G50" s="2">
-        <v>1.1900000000000001E-2</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="I50" s="2">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="J50" s="2">
-        <v>36.610199999999999</v>
+        <v>13.750999999999999</v>
       </c>
       <c r="K50" s="2">
-        <v>32.941600000000001</v>
+        <v>12.742100000000001</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="B51" s="2">
-        <v>102.5004</v>
+        <v>25.505199999999999</v>
       </c>
       <c r="C51" s="2">
-        <v>69.941699999999997</v>
+        <v>19.936499999999999</v>
       </c>
       <c r="E51" s="2">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="F51" s="2">
-        <v>183.66059999999999</v>
+        <v>53.217199999999998</v>
       </c>
       <c r="G51" s="2">
-        <v>2.3699999999999999E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="I51" s="2">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="J51" s="2">
-        <v>145.6395</v>
+        <v>36.610199999999999</v>
       </c>
       <c r="K51" s="2">
-        <v>132.96340000000001</v>
+        <v>32.941600000000001</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>32000</v>
+        <v>10000</v>
       </c>
       <c r="B52" s="2">
-        <v>395.53519999999997</v>
+        <v>42.646099999999997</v>
       </c>
       <c r="C52" s="2">
-        <v>271.66899999999998</v>
+        <v>28.490200000000002</v>
       </c>
       <c r="E52" s="2">
-        <v>32000</v>
+        <v>10000</v>
       </c>
       <c r="F52" s="2">
-        <v>761.73990000000003</v>
+        <v>77.169799999999995</v>
       </c>
       <c r="G52" s="2">
-        <v>8.1299999999999997E-2</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="I52" s="2">
-        <v>32000</v>
+        <v>10000</v>
       </c>
       <c r="J52" s="2">
-        <v>582.25909999999999</v>
+        <v>57.152900000000002</v>
       </c>
       <c r="K52" s="2">
-        <v>514.17470000000003</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>64000</v>
+        <v>15000</v>
       </c>
       <c r="B53" s="2">
-        <v>1647.6356000000001</v>
+        <v>87.357500000000002</v>
       </c>
       <c r="C53" s="2">
-        <v>1038.0461</v>
+        <v>60.469499999999996</v>
       </c>
       <c r="E53" s="2">
-        <v>64000</v>
+        <v>15000</v>
       </c>
       <c r="F53" s="2">
-        <v>3083.2289000000001</v>
+        <v>164.5008</v>
       </c>
       <c r="G53" s="2">
-        <v>9.3200000000000005E-2</v>
+        <v>2.1100000000000001E-2</v>
       </c>
       <c r="I53" s="2">
-        <v>64000</v>
+        <v>15000</v>
       </c>
       <c r="J53" s="2">
-        <v>2307.3020999999999</v>
+        <v>135.30269999999999</v>
       </c>
       <c r="K53" s="2">
-        <v>2096.8153000000002</v>
+        <v>111.6644</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
+        <v>16000</v>
+      </c>
+      <c r="B54" s="2">
+        <v>102.5004</v>
+      </c>
+      <c r="C54" s="2">
+        <v>69.941699999999997</v>
+      </c>
+      <c r="E54" s="2">
+        <v>16000</v>
+      </c>
+      <c r="F54" s="2">
+        <v>183.66059999999999</v>
+      </c>
+      <c r="G54" s="2">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="I54" s="2">
+        <v>16000</v>
+      </c>
+      <c r="J54" s="2">
+        <v>145.6395</v>
+      </c>
+      <c r="K54" s="2">
+        <v>132.96340000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>32000</v>
+      </c>
+      <c r="B55" s="2">
+        <v>395.53519999999997</v>
+      </c>
+      <c r="C55" s="2">
+        <v>271.66899999999998</v>
+      </c>
+      <c r="E55" s="2">
+        <v>32000</v>
+      </c>
+      <c r="F55" s="2">
+        <v>761.73990000000003</v>
+      </c>
+      <c r="G55" s="2">
+        <v>8.1299999999999997E-2</v>
+      </c>
+      <c r="I55" s="2">
+        <v>32000</v>
+      </c>
+      <c r="J55" s="2">
+        <v>582.25909999999999</v>
+      </c>
+      <c r="K55" s="2">
+        <v>514.17470000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>64000</v>
+      </c>
+      <c r="B56" s="2">
+        <v>1647.6356000000001</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1038.0461</v>
+      </c>
+      <c r="E56" s="2">
+        <v>64000</v>
+      </c>
+      <c r="F56" s="2">
+        <v>3083.2289000000001</v>
+      </c>
+      <c r="G56" s="2">
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="I56" s="2">
+        <v>64000</v>
+      </c>
+      <c r="J56" s="2">
+        <v>2307.3020999999999</v>
+      </c>
+      <c r="K56" s="2">
+        <v>2096.8153000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
         <v>128000</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B57" s="2">
         <v>6449.5387000000001</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C57" s="2">
         <v>4179.1432000000004</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E57" s="2">
         <v>128000</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F57" s="2">
         <v>13345.0816</v>
       </c>
-      <c r="G54" s="2">
+      <c r="G57" s="2">
         <v>0.27579999999999999</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I57" s="2">
         <v>128000</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J57" s="2">
         <v>9953.6134000000002</v>
       </c>
-      <c r="K54" s="2">
+      <c r="K57" s="2">
         <v>8372.7314999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="E71" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="I71" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>256000</v>
+      </c>
+      <c r="B58" s="2">
+        <v>26101.4016999999</v>
+      </c>
+      <c r="C58" s="2">
+        <v>16761.015299999999</v>
+      </c>
+      <c r="E58" s="2">
+        <v>256000</v>
+      </c>
+      <c r="F58" s="2">
+        <v>62985.170700000002</v>
+      </c>
+      <c r="G58" s="2">
+        <v>0.45529999999999998</v>
+      </c>
+      <c r="I58" s="2">
+        <v>256000</v>
+      </c>
+      <c r="J58" s="2">
+        <v>55569.639999999898</v>
+      </c>
+      <c r="K58" s="2">
+        <v>41101.481800000001</v>
+      </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="E92" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="I92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E72" s="2" t="s">
+      <c r="B93" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I72" s="2" t="s">
+      <c r="F93" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I93" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J72" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>76</v>
+      <c r="J93" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B94" s="2">
         <f>B48/B47</f>
         <v>3.510201715743102</v>
       </c>
-      <c r="C73" s="2">
-        <f>C48/C47</f>
+      <c r="C94" s="2">
+        <f t="shared" ref="C94:C104" si="0">C48/C47</f>
         <v>3.453662715978866</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="E94" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F73" s="2">
-        <f>F48/F47</f>
+      <c r="F94" s="2">
+        <f t="shared" ref="F94:G94" si="1">F48/F47</f>
         <v>2.900629539951574</v>
       </c>
-      <c r="G73" s="2">
-        <f>G48/G47</f>
+      <c r="G94" s="2">
+        <f t="shared" si="1"/>
         <v>1.6</v>
       </c>
-      <c r="I73" s="2" t="s">
+      <c r="I94" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J73" s="2">
-        <f>J48/J47</f>
+      <c r="J94" s="2">
+        <f t="shared" ref="J94:K94" si="2">J48/J47</f>
         <v>5.0685426819682435</v>
       </c>
-      <c r="K73" s="2">
-        <f>K48/K47</f>
+      <c r="K94" s="2">
+        <f t="shared" si="2"/>
         <v>1.9745408256046553</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B74" s="2">
-        <f>B49/B48</f>
+      <c r="B95" s="2">
+        <f t="shared" ref="B95:C95" si="3">B49/B48</f>
         <v>2.3922520558803133</v>
       </c>
-      <c r="C74" s="2">
-        <f>C49/C48</f>
+      <c r="C95" s="2">
+        <f t="shared" si="0"/>
         <v>2.1813859257421648</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F74" s="2">
-        <f>F49/F48</f>
+      <c r="F95" s="2">
+        <f t="shared" ref="F95:G95" si="4">F49/F48</f>
         <v>4.8483755718054029</v>
       </c>
-      <c r="G74" s="2">
-        <f>G49/G48</f>
+      <c r="G95" s="2">
+        <f t="shared" si="4"/>
         <v>1.90625</v>
       </c>
-      <c r="I74" s="2" t="s">
+      <c r="I95" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J74" s="2">
-        <f>J49/J48</f>
+      <c r="J95" s="2">
+        <f t="shared" ref="J95:K95" si="5">J49/J48</f>
         <v>2.9373158400794019</v>
       </c>
-      <c r="K74" s="2">
-        <f>K49/K48</f>
+      <c r="K95" s="2">
+        <f t="shared" si="5"/>
         <v>3.9630226561060962</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B96" s="2">
+        <f t="shared" ref="B96:C96" si="6">B50/B49</f>
+        <v>1.5176226962103956</v>
+      </c>
+      <c r="C96" s="2">
+        <f t="shared" si="0"/>
+        <v>1.6833905115714853</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F96" s="2">
+        <f t="shared" ref="F96:G96" si="7">F50/F49</f>
+        <v>1.3835638136690449</v>
+      </c>
+      <c r="G96" s="2">
+        <f t="shared" si="7"/>
+        <v>1.180327868852459</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J96" s="2">
+        <f t="shared" ref="J96:K96" si="8">J50/J49</f>
+        <v>1.4520284682477667</v>
+      </c>
+      <c r="K96" s="2">
+        <f t="shared" si="8"/>
+        <v>1.48058934941495</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B97" s="2">
+        <f t="shared" ref="B97:C97" si="9">B51/B50</f>
+        <v>2.3201520981724566</v>
+      </c>
+      <c r="C97" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2447474497263946</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F97" s="2">
+        <f t="shared" ref="F97:G97" si="10">F51/F50</f>
+        <v>2.6489529564607088</v>
+      </c>
+      <c r="G97" s="2">
+        <f t="shared" si="10"/>
+        <v>1.6527777777777779</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J97" s="2">
+        <f t="shared" ref="J97:K97" si="11">J51/J50</f>
+        <v>2.662366373354665</v>
+      </c>
+      <c r="K97" s="2">
+        <f t="shared" si="11"/>
+        <v>2.585256747317946</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B98" s="2">
+        <f t="shared" ref="B98:C98" si="12">B52/B51</f>
+        <v>1.6720551103304424</v>
+      </c>
+      <c r="C98" s="2">
+        <f t="shared" si="0"/>
+        <v>1.4290472249391821</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F98" s="2">
+        <f t="shared" ref="F98:G98" si="13">F52/F51</f>
+        <v>1.4500913238577</v>
+      </c>
+      <c r="G98" s="2">
+        <f t="shared" si="13"/>
+        <v>1.2857142857142856</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J98" s="2">
+        <f t="shared" ref="J98:K98" si="14">J52/J51</f>
+        <v>1.5611195786966474</v>
+      </c>
+      <c r="K98" s="2">
+        <f t="shared" si="14"/>
+        <v>1.5739976200305996</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B99" s="2">
+        <f t="shared" ref="B99:C99" si="15">B53/B52</f>
+        <v>2.0484288129512431</v>
+      </c>
+      <c r="C99" s="2">
+        <f t="shared" si="0"/>
+        <v>2.1224666727506296</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F99" s="2">
+        <f t="shared" ref="F99:G99" si="16">F53/F52</f>
+        <v>2.1316732711501132</v>
+      </c>
+      <c r="G99" s="2">
+        <f t="shared" si="16"/>
+        <v>1.3790849673202616</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J99" s="2">
+        <f t="shared" ref="J99:K99" si="17">J53/J52</f>
+        <v>2.3673811827571303</v>
+      </c>
+      <c r="K99" s="2">
+        <f t="shared" si="17"/>
+        <v>2.1536046287367405</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B100" s="2">
+        <f t="shared" ref="B100:C100" si="18">B54/B53</f>
+        <v>1.1733440173997653</v>
+      </c>
+      <c r="C100" s="2">
+        <f t="shared" si="0"/>
+        <v>1.1566442586758614</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F100" s="2">
+        <f t="shared" ref="F100:G100" si="19">F54/F53</f>
+        <v>1.1164723818972309</v>
+      </c>
+      <c r="G100" s="2">
+        <f t="shared" si="19"/>
+        <v>1.1232227488151658</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J100" s="2">
+        <f t="shared" ref="J100:K100" si="20">J54/J53</f>
+        <v>1.0763975885181893</v>
+      </c>
+      <c r="K100" s="2">
+        <f t="shared" si="20"/>
+        <v>1.1907411851942069</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B75" s="2">
-        <f>B50/B49</f>
-        <v>3.5211154828466897</v>
-      </c>
-      <c r="C75" s="2">
-        <f>C50/C49</f>
-        <v>3.7787865577437021</v>
-      </c>
-      <c r="E75" s="2" t="s">
+      <c r="B101" s="2">
+        <f t="shared" ref="B101:C101" si="21">B55/B54</f>
+        <v>3.8588649410148643</v>
+      </c>
+      <c r="C101" s="2">
+        <f t="shared" si="0"/>
+        <v>3.8842207152528463</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F75" s="2">
-        <f>F50/F49</f>
-        <v>3.6649954546706702</v>
-      </c>
-      <c r="G75" s="2">
-        <f>G50/G49</f>
-        <v>1.9508196721311475</v>
-      </c>
-      <c r="I75" s="2" t="s">
+      <c r="F101" s="2">
+        <f t="shared" ref="F101:G101" si="22">F55/F54</f>
+        <v>4.1475411710513859</v>
+      </c>
+      <c r="G101" s="2">
+        <f t="shared" si="22"/>
+        <v>3.4303797468354431</v>
+      </c>
+      <c r="I101" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J75" s="2">
-        <f>J50/J49</f>
-        <v>3.8658317670165361</v>
-      </c>
-      <c r="K75" s="2">
-        <f>K50/K49</f>
-        <v>3.8277036055820872</v>
+      <c r="J101" s="2">
+        <f t="shared" ref="J101:K101" si="23">J55/J54</f>
+        <v>3.9979476721631149</v>
+      </c>
+      <c r="K101" s="2">
+        <f t="shared" si="23"/>
+        <v>3.8670393506784575</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B76" s="2">
-        <f>B51/B50</f>
-        <v>4.0188040085943264</v>
-      </c>
-      <c r="C76" s="2">
-        <f>C51/C50</f>
-        <v>3.5082236099616284</v>
-      </c>
-      <c r="E76" s="2" t="s">
+      <c r="B102" s="2">
+        <f t="shared" ref="B102:C102" si="24">B56/B55</f>
+        <v>4.1655852627022831</v>
+      </c>
+      <c r="C102" s="2">
+        <f t="shared" si="0"/>
+        <v>3.8209957705884738</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F76" s="2">
-        <f>F51/F50</f>
-        <v>3.4511511315890351</v>
-      </c>
-      <c r="G76" s="2">
-        <f>G51/G50</f>
-        <v>1.991596638655462</v>
-      </c>
-      <c r="I76" s="2" t="s">
+      <c r="F102" s="2">
+        <f t="shared" ref="F102:G102" si="25">F56/F55</f>
+        <v>4.0476137589746841</v>
+      </c>
+      <c r="G102" s="2">
+        <f t="shared" si="25"/>
+        <v>1.1463714637146372</v>
+      </c>
+      <c r="I102" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J76" s="2">
-        <f>J51/J50</f>
-        <v>3.9781126571283414</v>
-      </c>
-      <c r="K76" s="2">
-        <f>K51/K50</f>
-        <v>4.0363370328095787</v>
+      <c r="J102" s="2">
+        <f t="shared" ref="J102:K102" si="26">J56/J55</f>
+        <v>3.9626724597348497</v>
+      </c>
+      <c r="K102" s="2">
+        <f t="shared" si="26"/>
+        <v>4.0780211472870995</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="2">
-        <f>B52/B51</f>
-        <v>3.8588649410148643</v>
-      </c>
-      <c r="C77" s="2">
-        <f>C52/C51</f>
-        <v>3.8842207152528463</v>
-      </c>
-      <c r="E77" s="2" t="s">
+      <c r="B103" s="2">
+        <f t="shared" ref="B103:C103" si="27">B57/B56</f>
+        <v>3.914420579404815</v>
+      </c>
+      <c r="C103" s="2">
+        <f t="shared" si="0"/>
+        <v>4.0259707155587794</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F77" s="2">
-        <f>F52/F51</f>
-        <v>4.1475411710513859</v>
-      </c>
-      <c r="G77" s="2">
-        <f>G52/G51</f>
-        <v>3.4303797468354431</v>
-      </c>
-      <c r="I77" s="2" t="s">
+      <c r="F103" s="2">
+        <f t="shared" ref="F103:G103" si="28">F57/F56</f>
+        <v>4.3282811730261086</v>
+      </c>
+      <c r="G103" s="2">
+        <f t="shared" si="28"/>
+        <v>2.9592274678111585</v>
+      </c>
+      <c r="I103" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J77" s="2">
-        <f>J52/J51</f>
-        <v>3.9979476721631149</v>
-      </c>
-      <c r="K77" s="2">
-        <f>K52/K51</f>
-        <v>3.8670393506784575</v>
+      <c r="J103" s="2">
+        <f t="shared" ref="J103:K103" si="29">J57/J56</f>
+        <v>4.3139619211545819</v>
+      </c>
+      <c r="K103" s="2">
+        <f t="shared" si="29"/>
+        <v>3.9930705866177143</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B78" s="2">
-        <f>B53/B52</f>
-        <v>4.1655852627022831</v>
-      </c>
-      <c r="C78" s="2">
-        <f>C53/C52</f>
-        <v>3.8209957705884738</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F78" s="2">
-        <f>F53/F52</f>
-        <v>4.0476137589746841</v>
-      </c>
-      <c r="G78" s="2">
-        <f>G53/G52</f>
-        <v>1.1463714637146372</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J78" s="2">
-        <f>J53/J52</f>
-        <v>3.9626724597348497</v>
-      </c>
-      <c r="K78" s="2">
-        <f>K53/K52</f>
-        <v>4.0780211472870995</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B79" s="2">
-        <f>B54/B53</f>
-        <v>3.914420579404815</v>
-      </c>
-      <c r="C79" s="2">
-        <f>C54/C53</f>
-        <v>4.0259707155587794</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F79" s="2">
-        <f>F54/F53</f>
-        <v>4.3282811730261086</v>
-      </c>
-      <c r="G79" s="2">
-        <f>G54/G53</f>
-        <v>2.9592274678111585</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J79" s="2">
-        <f>J54/J53</f>
-        <v>4.3139619211545819</v>
-      </c>
-      <c r="K79" s="2">
-        <f>K54/K53</f>
-        <v>3.9930705866177143</v>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="2">
+        <f t="shared" ref="B104:C104" si="30">B58/B57</f>
+        <v>4.0470183859816053</v>
+      </c>
+      <c r="C104" s="2">
+        <f t="shared" si="0"/>
+        <v>4.01063435682223</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F104" s="2">
+        <f t="shared" ref="F104:G104" si="31">F58/F57</f>
+        <v>4.7197291547471698</v>
+      </c>
+      <c r="G104" s="2">
+        <f t="shared" si="31"/>
+        <v>1.6508339376359682</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J104" s="2">
+        <f t="shared" ref="J104:K104" si="32">J58/J57</f>
+        <v>5.5828609939783167</v>
+      </c>
+      <c r="K104" s="2">
+        <f t="shared" si="32"/>
+        <v>4.9089692891740286</v>
       </c>
     </row>
   </sheetData>
